--- a/data/grades/analyse.xlsx
+++ b/data/grades/analyse.xlsx
@@ -1,43 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillaumemetzler/Documents/GuillaumeMetzler.github.io/data/grades/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A69892-089A-7644-986E-CFCCB7F8D4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="notes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+  <si>
+    <t>annee</t>
+  </si>
+  <si>
+    <t>Contrôle 1</t>
+  </si>
+  <si>
+    <t>Contrôle 2</t>
+  </si>
+  <si>
+    <t>Moyenne</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="-webkit-standard"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -45,88 +101,188 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -414,31 +570,693 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>annee</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16" thickBot="1">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="5">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="D2" s="5">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4">
+        <f>AVERAGE(LARGE(B2:D2,1),LARGE(B2:D2,2))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" ref="E3:E5" si="0">AVERAGE(LARGE(B3:D3,1),LARGE(B3:D3,2))</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>16</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="D5" s="3">
+        <v>19</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="0"/>
+        <v>13.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="3">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>18</v>
+      </c>
+      <c r="E6" s="10">
+        <f>AVERAGE(LARGE(B6:D6,1),LARGE(B6:D6,2))</f>
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>12</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" ref="E7:E37" si="1">AVERAGE(LARGE(B7:D7,1),LARGE(B7:D7,2))</f>
+        <v>6.125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>14</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="3">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>13</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>16</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>15</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>14</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="1"/>
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3">
+        <v>12</v>
+      </c>
+      <c r="D18" s="3">
+        <v>18</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="10">
+        <f t="shared" si="1"/>
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4</v>
+      </c>
+      <c r="E20" s="10">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="D21" s="3">
+        <v>18</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="1"/>
+        <v>12.625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="1"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" s="10">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>15</v>
+      </c>
+      <c r="E25" s="10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>12</v>
+      </c>
+      <c r="E26" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3</v>
+      </c>
+      <c r="D27" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="E27" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="D28" s="3">
+        <v>18</v>
+      </c>
+      <c r="E28" s="10">
+        <f t="shared" si="1"/>
+        <v>10.375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D29" s="3">
+        <v>17</v>
+      </c>
+      <c r="E29" s="10">
+        <f t="shared" si="1"/>
+        <v>8.625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D30" s="3">
+        <v>15</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" si="1"/>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="C31" s="3">
+        <v>16</v>
+      </c>
+      <c r="D31" s="3">
+        <v>19</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="3">
+        <v>18</v>
+      </c>
+      <c r="E32" s="10">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="3">
+        <v>13</v>
+      </c>
+      <c r="E33" s="10">
+        <f t="shared" si="1"/>
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>12</v>
+      </c>
+      <c r="E34" s="10">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="3">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>13</v>
+      </c>
+      <c r="E35" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="3">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D36" s="3">
+        <v>19</v>
+      </c>
+      <c r="E36" s="10">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" thickBot="1">
+      <c r="A37" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="12">
+        <v>0</v>
+      </c>
+      <c r="C37" s="12">
+        <v>0</v>
+      </c>
+      <c r="D37" s="12">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B37">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$U2=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C37">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$V2=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D37">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$W2=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/grades/analyse.xlsx
+++ b/data/grades/analyse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillaumemetzler/Documents/GuillaumeMetzler.github.io/data/grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A69892-089A-7644-986E-CFCCB7F8D4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41DF5E7-4D43-7046-9BB0-1EBA1CF7F113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>annee</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Contrôle 2</t>
+  </si>
+  <si>
+    <t>Contrôle 3</t>
   </si>
   <si>
     <t>Moyenne</t>
@@ -93,39 +96,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -138,21 +113,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -196,21 +156,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -221,35 +166,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,7 +537,7 @@
     <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="16" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,23 +548,23 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="10">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" thickBot="1">
-      <c r="A2">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="5">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="C2" s="10">
         <v>1.25</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="10">
         <v>18</v>
       </c>
       <c r="E2" s="4">
@@ -614,629 +573,631 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="C3" s="9">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
         <f t="shared" ref="E3:E5" si="0">AVERAGE(LARGE(B3:D3,1),LARGE(B3:D3,2))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="9">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="9">
         <v>2.25</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="9">
         <v>16</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="6">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="9">
         <v>7.5</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="9">
         <v>7.75</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="9">
         <v>19</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="6">
         <f t="shared" si="0"/>
         <v>13.375</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="9">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="9">
         <v>15.5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="9">
         <v>18</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="6">
         <f>AVERAGE(LARGE(B6:D6,1),LARGE(B6:D6,2))</f>
         <v>16.75</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
+      <c r="A7" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
         <v>0.25</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="9">
         <v>12</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="6">
         <f t="shared" ref="E7:E37" si="1">AVERAGE(LARGE(B7:D7,1),LARGE(B7:D7,2))</f>
         <v>6.125</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="9">
         <v>15.5</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="9">
         <v>14.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="9">
         <v>19.5</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="6">
         <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="9">
         <v>7</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="9">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="9">
         <v>14</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="6">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="9">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
         <v>7</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="9">
         <v>5</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="9">
         <v>3</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="9">
         <v>13</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="6">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="9">
         <v>9</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="9">
         <v>3</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="9">
         <v>16</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="6">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="A13" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
         <v>15</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="6">
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="9">
         <v>9</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="9">
         <v>7</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="9">
         <v>14</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="6">
         <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="A15" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
         <v>16.5</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="6">
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="A16" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
         <v>0.5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="9">
         <v>15</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="6">
         <f t="shared" si="1"/>
         <v>7.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="A17" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="9">
         <v>11</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="9">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="9">
         <v>18</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="A19" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
         <v>0.25</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="9">
         <v>3</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="6">
         <f t="shared" si="1"/>
         <v>1.625</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="9">
         <v>0.5</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="9">
         <v>0.5</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="9">
         <v>4</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="6">
         <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B21" s="3">
+      <c r="A21" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="9">
         <v>3</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="9">
         <v>7.25</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="9">
         <v>18</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="6">
         <f t="shared" si="1"/>
         <v>12.625</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="9">
         <v>3.5</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="9">
         <v>0.25</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="9">
         <v>8</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="6">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="A23" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="9">
         <v>5.5</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="9">
         <v>1</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="9">
         <v>11</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="6">
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="A24" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
         <v>0.5</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="9">
         <v>12</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="6">
         <f t="shared" si="1"/>
         <v>6.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B25" s="3">
+      <c r="A25" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="9">
         <v>3</v>
       </c>
-      <c r="C25" s="3">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
         <v>15</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="6">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="A26" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
         <v>12</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B27" s="3">
+      <c r="A27" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="9">
         <v>6.5</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="9">
         <v>3</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="9">
         <v>13.5</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="6">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B28" s="3">
+      <c r="A28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="9">
         <v>0.5</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="9">
         <v>2.75</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="9">
         <v>18</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="6">
         <f t="shared" si="1"/>
         <v>10.375</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="A29" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
         <v>0.25</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="9">
         <v>17</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="6">
         <f t="shared" si="1"/>
         <v>8.625</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B30" s="3">
+      <c r="A30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="9">
         <v>1</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="9">
         <v>2.5</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="9">
         <v>15</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="6">
         <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B31" s="3">
+      <c r="A31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="9">
         <v>4.5</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="9">
         <v>16</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="9">
         <v>19</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="6">
         <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B32" s="3">
+      <c r="A32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="9">
         <v>1</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="9">
         <v>0.5</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="9">
         <v>18</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="6">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B33" s="3">
+      <c r="A33" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="9">
         <v>2</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="9">
         <v>2.5</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="9">
         <v>13</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="6">
         <f t="shared" si="1"/>
         <v>7.75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B34" s="3">
+      <c r="A34" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="9">
         <v>0.5</v>
       </c>
-      <c r="C34" s="3">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
         <v>12</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="6">
         <f t="shared" si="1"/>
         <v>6.25</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B35" s="3">
+      <c r="A35" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="9">
         <v>5</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="9">
         <v>7</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="9">
         <v>13</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="6">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="9">
-        <v>2026</v>
-      </c>
-      <c r="B36" s="3">
+      <c r="A36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="9">
         <v>14</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="9">
         <v>12.5</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="9">
         <v>19</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="6">
         <f t="shared" si="1"/>
         <v>16.5</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" thickBot="1">
-      <c r="A37" s="11">
-        <v>2026</v>
-      </c>
-      <c r="B37" s="12">
-        <v>0</v>
-      </c>
-      <c r="C37" s="12">
-        <v>0</v>
-      </c>
-      <c r="D37" s="12">
+      <c r="A37" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="11">
+        <v>0</v>
+      </c>
+      <c r="C37" s="11">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11">
         <v>13</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="8">
         <f t="shared" si="1"/>
         <v>6.5</v>
       </c>
